--- a/artfynd/A 49491-2024 artfynd.xlsx
+++ b/artfynd/A 49491-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122800306</v>
+        <v>122800307</v>
       </c>
       <c r="B2" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>734224</v>
+        <v>734195</v>
       </c>
       <c r="R2" t="n">
-        <v>7413159</v>
+        <v>7413167</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122800307</v>
+        <v>122800308</v>
       </c>
       <c r="B3" t="n">
-        <v>78762</v>
+        <v>82553</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>734195</v>
+        <v>734259</v>
       </c>
       <c r="R3" t="n">
-        <v>7413167</v>
+        <v>7413180</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -861,6 +861,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -879,10 +880,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122800308</v>
+        <v>122800306</v>
       </c>
       <c r="B4" t="n">
-        <v>82549</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +896,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>734259</v>
+        <v>734224</v>
       </c>
       <c r="R4" t="n">
-        <v>7413180</v>
+        <v>7413159</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -963,7 +964,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49491-2024 artfynd.xlsx
+++ b/artfynd/A 49491-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122800308</v>
+        <v>122800306</v>
       </c>
       <c r="B3" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>734259</v>
+        <v>734224</v>
       </c>
       <c r="R3" t="n">
-        <v>7413180</v>
+        <v>7413159</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -861,7 +861,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -880,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122800306</v>
+        <v>122800308</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>82553</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -920,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>734224</v>
+        <v>734259</v>
       </c>
       <c r="R4" t="n">
-        <v>7413159</v>
+        <v>7413180</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -964,6 +963,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49491-2024 artfynd.xlsx
+++ b/artfynd/A 49491-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122800307</v>
+        <v>122800308</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>82553</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>734195</v>
+        <v>734259</v>
       </c>
       <c r="R2" t="n">
-        <v>7413167</v>
+        <v>7413180</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,6 +759,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,7 +778,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122800306</v>
+        <v>122800307</v>
       </c>
       <c r="B3" t="n">
         <v>78766</v>
@@ -817,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>734224</v>
+        <v>734195</v>
       </c>
       <c r="R3" t="n">
-        <v>7413159</v>
+        <v>7413167</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +880,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122800308</v>
+        <v>122800306</v>
       </c>
       <c r="B4" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +896,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>734259</v>
+        <v>734224</v>
       </c>
       <c r="R4" t="n">
-        <v>7413180</v>
+        <v>7413159</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -963,7 +964,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49491-2024 artfynd.xlsx
+++ b/artfynd/A 49491-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122800308</v>
+        <v>122800306</v>
       </c>
       <c r="B2" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>734259</v>
+        <v>734224</v>
       </c>
       <c r="R2" t="n">
-        <v>7413180</v>
+        <v>7413159</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -778,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122800307</v>
+        <v>122800308</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>82553</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -818,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>734195</v>
+        <v>734259</v>
       </c>
       <c r="R3" t="n">
-        <v>7413167</v>
+        <v>7413180</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,6 +861,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -880,7 +880,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122800306</v>
+        <v>122800307</v>
       </c>
       <c r="B4" t="n">
         <v>78766</v>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>734224</v>
+        <v>734195</v>
       </c>
       <c r="R4" t="n">
-        <v>7413159</v>
+        <v>7413167</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 49491-2024 artfynd.xlsx
+++ b/artfynd/A 49491-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122800308</v>
+        <v>122800307</v>
       </c>
       <c r="B3" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>734259</v>
+        <v>734195</v>
       </c>
       <c r="R3" t="n">
-        <v>7413180</v>
+        <v>7413167</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -861,7 +861,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -880,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122800307</v>
+        <v>122800308</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>82553</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -920,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>734195</v>
+        <v>734259</v>
       </c>
       <c r="R4" t="n">
-        <v>7413167</v>
+        <v>7413180</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -964,6 +963,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49491-2024 artfynd.xlsx
+++ b/artfynd/A 49491-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122800306</v>
+        <v>122800307</v>
       </c>
       <c r="B2" t="n">
         <v>78766</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>734224</v>
+        <v>734195</v>
       </c>
       <c r="R2" t="n">
-        <v>7413159</v>
+        <v>7413167</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122800307</v>
+        <v>122800308</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>82553</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>734195</v>
+        <v>734259</v>
       </c>
       <c r="R3" t="n">
-        <v>7413167</v>
+        <v>7413180</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -861,6 +861,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -879,10 +880,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122800308</v>
+        <v>122800306</v>
       </c>
       <c r="B4" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +896,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>734259</v>
+        <v>734224</v>
       </c>
       <c r="R4" t="n">
-        <v>7413180</v>
+        <v>7413159</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -963,7 +964,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49491-2024 artfynd.xlsx
+++ b/artfynd/A 49491-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122800307</v>
+        <v>122800306</v>
       </c>
       <c r="B2" t="n">
         <v>78766</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>734195</v>
+        <v>734224</v>
       </c>
       <c r="R2" t="n">
-        <v>7413167</v>
+        <v>7413159</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122800308</v>
+        <v>122800307</v>
       </c>
       <c r="B3" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>734259</v>
+        <v>734195</v>
       </c>
       <c r="R3" t="n">
-        <v>7413180</v>
+        <v>7413167</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -861,7 +861,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -880,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122800306</v>
+        <v>122800308</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>82553</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -920,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>734224</v>
+        <v>734259</v>
       </c>
       <c r="R4" t="n">
-        <v>7413159</v>
+        <v>7413180</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -964,6 +963,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49491-2024 artfynd.xlsx
+++ b/artfynd/A 49491-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122800306</v>
+        <v>122800308</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>82556</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>734224</v>
+        <v>734259</v>
       </c>
       <c r="R2" t="n">
-        <v>7413159</v>
+        <v>7413180</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,6 +759,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,10 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122800307</v>
+        <v>122800306</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>734195</v>
+        <v>734224</v>
       </c>
       <c r="R3" t="n">
-        <v>7413167</v>
+        <v>7413159</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +880,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122800308</v>
+        <v>122800307</v>
       </c>
       <c r="B4" t="n">
-        <v>82553</v>
+        <v>78769</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +896,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>734259</v>
+        <v>734195</v>
       </c>
       <c r="R4" t="n">
-        <v>7413180</v>
+        <v>7413167</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -963,7 +964,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49491-2024 artfynd.xlsx
+++ b/artfynd/A 49491-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122800308</v>
+        <v>122800306</v>
       </c>
       <c r="B2" t="n">
-        <v>82556</v>
+        <v>78771</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>734259</v>
+        <v>734224</v>
       </c>
       <c r="R2" t="n">
-        <v>7413180</v>
+        <v>7413159</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -778,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122800306</v>
+        <v>122800307</v>
       </c>
       <c r="B3" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>734224</v>
+        <v>734195</v>
       </c>
       <c r="R3" t="n">
-        <v>7413159</v>
+        <v>7413167</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -880,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122800307</v>
+        <v>122800308</v>
       </c>
       <c r="B4" t="n">
-        <v>78769</v>
+        <v>82558</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -920,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>734195</v>
+        <v>734259</v>
       </c>
       <c r="R4" t="n">
-        <v>7413167</v>
+        <v>7413180</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -964,6 +963,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49491-2024 artfynd.xlsx
+++ b/artfynd/A 49491-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122800306</v>
       </c>
       <c r="B2" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>122800307</v>
       </c>
       <c r="B3" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>122800308</v>
       </c>
       <c r="B4" t="n">
-        <v>82558</v>
+        <v>82559</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 49491-2024 artfynd.xlsx
+++ b/artfynd/A 49491-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122800306</v>
       </c>
       <c r="B2" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>122800307</v>
       </c>
       <c r="B3" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>122800308</v>
       </c>
       <c r="B4" t="n">
-        <v>82559</v>
+        <v>82562</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
